--- a/ComponentesMetodologicos/Nuevo Hoja de cálculo de Microsoft Excel.xlsx
+++ b/ComponentesMetodologicos/Nuevo Hoja de cálculo de Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Desktop\CEREBRUM\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BCA722-EED6-4C96-B8B2-9DDFED71B69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B770D3-9D1F-412D-AD56-1DAE5179C8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,37 +28,500 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">cuenta </t>
-  </si>
-  <si>
-    <t>institucion</t>
-  </si>
-  <si>
-    <t>correo</t>
-  </si>
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre Estudiante </t>
-  </si>
-  <si>
-    <t>telefono</t>
-  </si>
-  <si>
-    <t>documento</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>Institución</t>
+  </si>
+  <si>
+    <t>Materia</t>
+  </si>
+  <si>
+    <t>Tema</t>
+  </si>
+  <si>
+    <t>Subtema</t>
+  </si>
+  <si>
+    <t>Nombre_Estudiante</t>
+  </si>
+  <si>
+    <t>CU001</t>
+  </si>
+  <si>
+    <t>Ian Santiago Fernández Amaya</t>
+  </si>
+  <si>
+    <t>Colegio San José</t>
+  </si>
+  <si>
+    <t>CU002</t>
+  </si>
+  <si>
+    <t>Andrea Colmenares</t>
+  </si>
+  <si>
+    <t>Colegio La Esperanza</t>
+  </si>
+  <si>
+    <t>CU003</t>
+  </si>
+  <si>
+    <t>Joseph Andrés Rivas Sánchez</t>
+  </si>
+  <si>
+    <t>CU004</t>
+  </si>
+  <si>
+    <t>Pedro Eustaquio Pérez Silva</t>
+  </si>
+  <si>
+    <t>Instituto Técnico Central</t>
+  </si>
+  <si>
+    <t>CU005</t>
+  </si>
+  <si>
+    <t>María Fernanda León Quintana</t>
+  </si>
+  <si>
+    <t>Colegio Santa María</t>
+  </si>
+  <si>
+    <t>CU006</t>
+  </si>
+  <si>
+    <t>Sebastián Camilo Blandón Espitia</t>
+  </si>
+  <si>
+    <t>CU007</t>
+  </si>
+  <si>
+    <t>Jorge Andrés Fernández Amaya</t>
+  </si>
+  <si>
+    <t>Colegio Nueva Granada</t>
+  </si>
+  <si>
+    <t>CU008</t>
+  </si>
+  <si>
+    <t>Rossana Amaya</t>
+  </si>
+  <si>
+    <t>Colegio Distrital El Porvenir</t>
+  </si>
+  <si>
+    <t>CU009</t>
+  </si>
+  <si>
+    <t>Gabriel Fernández</t>
+  </si>
+  <si>
+    <t>SENA</t>
+  </si>
+  <si>
+    <t>CU010</t>
+  </si>
+  <si>
+    <t>Samantha Loaiza</t>
+  </si>
+  <si>
+    <t>CU011</t>
+  </si>
+  <si>
+    <t>Anderson Exnehider Cunacue</t>
+  </si>
+  <si>
+    <t>Colegio San Martín</t>
+  </si>
+  <si>
+    <t>CU012</t>
+  </si>
+  <si>
+    <t>Iván Martínez</t>
+  </si>
+  <si>
+    <t>Colegio Los Andes</t>
+  </si>
+  <si>
+    <t>CU013</t>
+  </si>
+  <si>
+    <t>Juan Esteban Hoyos Torres</t>
+  </si>
+  <si>
+    <t>CU014</t>
+  </si>
+  <si>
+    <t>Karen Dayana Rivera Castro</t>
+  </si>
+  <si>
+    <t>Colegio Nuestra Señora</t>
+  </si>
+  <si>
+    <t>CU015</t>
+  </si>
+  <si>
+    <t>Isai Lora</t>
+  </si>
+  <si>
+    <t>Universidad Distrital</t>
+  </si>
+  <si>
+    <t>CU016</t>
+  </si>
+  <si>
+    <t>Ana Verónica Amaya Contreras</t>
+  </si>
+  <si>
+    <t>CU017</t>
+  </si>
+  <si>
+    <t>John Alexander Peña</t>
+  </si>
+  <si>
+    <t>Colegio San Rafael</t>
+  </si>
+  <si>
+    <t>CU018</t>
+  </si>
+  <si>
+    <t>Luis Alejandro Matoma Bocanegra</t>
+  </si>
+  <si>
+    <t>Institución Educativa El Carmen</t>
+  </si>
+  <si>
+    <t>CU019</t>
+  </si>
+  <si>
+    <t>Sebastián Córdoba</t>
+  </si>
+  <si>
+    <t>ian.fernandez@mail.com</t>
+  </si>
+  <si>
+    <t>andrea.colmenares@mail.com</t>
+  </si>
+  <si>
+    <t>joseph.rivas@mail.com</t>
+  </si>
+  <si>
+    <t>rossana.amaya@mail.com</t>
+  </si>
+  <si>
+    <t>gabriel.fernandez@mail.com</t>
+  </si>
+  <si>
+    <t>samantha.loaiza@mail.com</t>
+  </si>
+  <si>
+    <t>jorge.fernandez@mail.com</t>
+  </si>
+  <si>
+    <t>anderson.cunacue@mail.com</t>
+  </si>
+  <si>
+    <t>ivan.martinez@mail.com</t>
+  </si>
+  <si>
+    <t>juan.hoyos@mail.com</t>
+  </si>
+  <si>
+    <t>karen.rivera@mail.com</t>
+  </si>
+  <si>
+    <t>isai.lora@mail.com</t>
+  </si>
+  <si>
+    <t>ana.amaya@mail.com</t>
+  </si>
+  <si>
+    <t>john.pena@mail.com</t>
+  </si>
+  <si>
+    <t>luis.matoma@mail.com</t>
+  </si>
+  <si>
+    <t>sebastian.cordoba@mail.com</t>
+  </si>
+  <si>
+    <t>Ninguna</t>
+  </si>
+  <si>
+    <t>sebastian.blandon@mail.com</t>
+  </si>
+  <si>
+    <t>maria.leon@mail.com</t>
+  </si>
+  <si>
+    <t>pedro.perez@mail.com</t>
+  </si>
+  <si>
+    <t>TI-1001001001</t>
+  </si>
+  <si>
+    <t>CC-1001001015</t>
+  </si>
+  <si>
+    <t>CC-1001001014</t>
+  </si>
+  <si>
+    <t>CC-1001001013</t>
+  </si>
+  <si>
+    <t>CC-1001001012</t>
+  </si>
+  <si>
+    <t>CC-1001001011</t>
+  </si>
+  <si>
+    <t>CC--1001001010</t>
+  </si>
+  <si>
+    <t>PPT-1001001009</t>
+  </si>
+  <si>
+    <t>PPT-1001001008</t>
+  </si>
+  <si>
+    <t>PPT-1001001007</t>
+  </si>
+  <si>
+    <t>CC-1001001006</t>
+  </si>
+  <si>
+    <t>CC-1001001005</t>
+  </si>
+  <si>
+    <t>TI-1001001004</t>
+  </si>
+  <si>
+    <t>CEM-1001001002</t>
+  </si>
+  <si>
+    <t>CC-1001001003</t>
+  </si>
+  <si>
+    <t>CEM-1001001016</t>
+  </si>
+  <si>
+    <t>CC-1001001017</t>
+  </si>
+  <si>
+    <t>CC-1001001018</t>
+  </si>
+  <si>
+    <t>TI-1001001019</t>
+  </si>
+  <si>
+    <t>Matemáticas, Física, Inglés</t>
+  </si>
+  <si>
+    <t>Lenguaje, Historia</t>
+  </si>
+  <si>
+    <t>Química, Matemáticas, Física</t>
+  </si>
+  <si>
+    <t>Matemáticas, Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>Inglés, Lenguaje, Historia</t>
+  </si>
+  <si>
+    <t>Física, Química</t>
+  </si>
+  <si>
+    <t>Matemáticas, Inglés, Física</t>
+  </si>
+  <si>
+    <t>Historia, Lenguaje</t>
+  </si>
+  <si>
+    <t>Programación, Matemáticas, Física</t>
+  </si>
+  <si>
+    <t>Química, Inglés, Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>Física, Matemáticas</t>
+  </si>
+  <si>
+    <t>Matemáticas, Química, Historia</t>
+  </si>
+  <si>
+    <t>Inglés, Ciencias Naturales, Lenguaje</t>
+  </si>
+  <si>
+    <t>Lenguaje, Inglés</t>
+  </si>
+  <si>
+    <t>Historia, Química, Matemáticas</t>
+  </si>
+  <si>
+    <t>Matemáticas, Física</t>
+  </si>
+  <si>
+    <t>Lenguaje, Historia, Inglés</t>
+  </si>
+  <si>
+    <t>Química, Matemáticas, Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>Álgebra, Movimiento, Gramática</t>
+  </si>
+  <si>
+    <t>Ecuaciones, Velocidad, Verbos</t>
+  </si>
+  <si>
+    <t>Literatura, Colombia</t>
+  </si>
+  <si>
+    <t>Géneros literarios, Constitución de 1991</t>
+  </si>
+  <si>
+    <t>Materia, Geometría, Energía</t>
+  </si>
+  <si>
+    <t>Propiedades físicas, Ángulos, Energía cinética</t>
+  </si>
+  <si>
+    <t>Estadística, Biología</t>
+  </si>
+  <si>
+    <t>Media aritmética, La célula</t>
+  </si>
+  <si>
+    <t>Gramática, Comprensión lectora, Edad Moderna</t>
+  </si>
+  <si>
+    <t>Verbos irregulares, Idea principal, Renacimiento</t>
+  </si>
+  <si>
+    <t>Fuerzas, Reacciones químicas</t>
+  </si>
+  <si>
+    <t>Leyes de Newton, Balanceo de ecuaciones</t>
+  </si>
+  <si>
+    <t>Trigonometría, Vocabulario, Movimiento</t>
+  </si>
+  <si>
+    <t>Seno y coseno, Vida cotidiana, Aceleración</t>
+  </si>
+  <si>
+    <t>Colombia, Literatura</t>
+  </si>
+  <si>
+    <t>Independencia, Géneros literarios</t>
+  </si>
+  <si>
+    <t>Algoritmos, Álgebra, Energía</t>
+  </si>
+  <si>
+    <t>Condicionales, Ecuaciones, Energía cinética</t>
+  </si>
+  <si>
+    <t>Tabla periódica, Gramática, Ecología</t>
+  </si>
+  <si>
+    <t>Grupos y períodos, Tiempos verbales, Ecosistemas</t>
+  </si>
+  <si>
+    <t>Fuerzas, Geometría</t>
+  </si>
+  <si>
+    <t>Leyes de Newton, Triángulos</t>
+  </si>
+  <si>
+    <t>Trigonometría, Materia, Colombia</t>
+  </si>
+  <si>
+    <t>Seno y coseno, Propiedades, Constitución</t>
+  </si>
+  <si>
+    <t>Vocabulario, Biología, Argumentación</t>
+  </si>
+  <si>
+    <t>Vida cotidiana, La célula, Tesis</t>
+  </si>
+  <si>
+    <t>Comprensión lectora, Gramática</t>
+  </si>
+  <si>
+    <t>Idea principal, Verbos</t>
+  </si>
+  <si>
+    <t>Edad Moderna, Reacciones químicas, Estadística</t>
+  </si>
+  <si>
+    <t>Renacimiento, Balanceo, Probabilidad</t>
+  </si>
+  <si>
+    <t>Probabilidad, Movimiento</t>
+  </si>
+  <si>
+    <t>Eventos, Velocidad</t>
+  </si>
+  <si>
+    <t>Argumentación, Colombia, Vocabulario</t>
+  </si>
+  <si>
+    <t>Tesis, Independencia, Vida cotidiana</t>
+  </si>
+  <si>
+    <t>Energía, Reacciones químicas</t>
+  </si>
+  <si>
+    <t>Energía cinética, Balanceo</t>
+  </si>
+  <si>
+    <t>Tabla periódica, Álgebra, Ecología</t>
+  </si>
+  <si>
+    <t>Grupos y períodos, Ecuaciones, Ecosistemas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -72,7 +535,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -80,14 +543,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -366,39 +869,863 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3104567821</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3115678932</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D4" s="6">
+        <v>3126789043</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3137890154</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3148901265</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D7" s="6">
+        <v>3159012376</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3160123487</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D9" s="6">
+        <v>3171234598</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3182345609</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D11" s="6">
+        <v>3193456710</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3004567821</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3015678932</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3026789043</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="6">
+        <v>3037890154</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D16" s="6">
+        <v>3048901265</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3059012376</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3060123487</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3071234598</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3082345609</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{9EC690EE-D698-44C2-B7FD-E8CBD7E91E58}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{B728C904-B6A5-49C5-AF7B-EE39C9C5C74F}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{B99BCAED-8C4C-483D-ADBA-E239A5628DC7}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{F6146A0E-DA55-4769-B4D1-9506006669E1}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{A60776F3-60C4-42FD-8C73-64C6D7084283}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{3E43A162-EB31-4517-A8CB-86817302621F}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{10121357-CCCA-4F37-99C8-674D7F03A989}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{89EA8F79-1871-4312-8534-C300D483AD68}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{BCD1E6CF-BD9D-4A5E-9E38-35CE0C0D22FE}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{B29220C0-9DC8-42AE-8128-D5BB36FA6626}"/>
+    <hyperlink ref="F16" r:id="rId11" xr:uid="{253B6AC2-7E54-467F-9E65-35F5F874AAC4}"/>
+    <hyperlink ref="F17" r:id="rId12" xr:uid="{80053957-03B1-4503-8A36-5ABBB2AC3D0F}"/>
+    <hyperlink ref="F18" r:id="rId13" xr:uid="{F17AF9DD-A824-4D05-9708-678402DC0BE1}"/>
+    <hyperlink ref="F19" r:id="rId14" xr:uid="{DCF70C54-87FC-42FF-B13B-423BB0A40E9B}"/>
+    <hyperlink ref="F20" r:id="rId15" xr:uid="{8CD2AF1F-E17F-461F-8BBF-782D897E4DFE}"/>
+    <hyperlink ref="F7" r:id="rId16" xr:uid="{D00711D3-D5BC-494F-9DD6-B08783DBA130}"/>
+    <hyperlink ref="F6" r:id="rId17" xr:uid="{7600D247-658C-49E0-BADE-09C195F18778}"/>
+    <hyperlink ref="F5" r:id="rId18" xr:uid="{21DE4229-5E8F-4961-BCCA-5736A09E6CE3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId19"/>
 </worksheet>
 </file>